--- a/public/Guia/AutDeRei-CuentasConceptos.xlsx
+++ b/public/Guia/AutDeRei-CuentasConceptos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dmijangos\Documents\SAC-IPE\public\Guia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76B588C8-582C-4D5A-BA32-03676C639D1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7183E36-5F5D-41B0-BFCE-6B80A3FAA06F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BA794CD9-A794-4D6D-97A5-04484BD59B08}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="21">
   <si>
     <t>cuenta</t>
   </si>
@@ -96,6 +96,9 @@
   </si>
   <si>
     <t>Por la autorización del reintegro a la Tesorería de ingresos de subsidios y subvenciones, en términos de las disposiciones aplicables.</t>
+  </si>
+  <si>
+    <t>Por la autorización del reintegro a la Tesorería de ingresos de aportaciones, en términos de las disposiciones aplicables</t>
   </si>
 </sst>
 </file>
@@ -577,7 +580,7 @@
         <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D8" t="s">
         <v>9</v>
@@ -592,7 +595,7 @@
         <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D9" t="s">
         <v>9</v>
@@ -634,7 +637,7 @@
         <v>14</v>
       </c>
       <c r="C12" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D12" t="s">
         <v>5</v>
@@ -648,7 +651,7 @@
         <v>14</v>
       </c>
       <c r="C13" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D13" t="s">
         <v>5</v>
@@ -690,7 +693,7 @@
         <v>14</v>
       </c>
       <c r="C16" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D16" t="s">
         <v>4</v>
@@ -704,7 +707,7 @@
         <v>14</v>
       </c>
       <c r="C17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D17" t="s">
         <v>4</v>
